--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examinationsformer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Examinationsformer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Examinationsformer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examinationsformer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 **examineras genom en skriftlig rapport med problemformulering, syfte, frågeställningar, forskningsbakgrund …</t>
+          <t>Examinationsformer skrivet som löpande text: **Delkurs 1** examineras genom en skriftlig rapport med problemformulering, syfte, frågeställningar, forskningsbakgrund …</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Modul 1 **examineras genom muntliga presentationer, samt en ‘pitch‘ av ett konceptförslag. **Modul 2** examineras geno…</t>
+          <t>Examinationsformer skrivet som löpande text: **Modul 1** examineras genom muntliga presentationer, samt en ‘pitch‘ av ett konceptförslag. **Modul 2** examineras geno…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Alla delkurser examineras genom aktivt seminariedeltagande och olika skriftliga inlämningsuppgifter. **Delkurs 1 **exami…</t>
+          <t>Examinationsformer skrivet som löpande text: Alla delkurser examineras genom aktivt seminariedeltagande och olika skriftliga inlämningsuppgifter. **Delkurs 1** exami…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 **examineras genom en skriftlig tentamen. **Delkurs 2 **examineras genom en skriftlig inlämningsuppgift som …</t>
+          <t>Examinationsformer skrivet som löpande text: **Delkurs 1** examineras genom en skriftlig tentamen. **Delkurs 2** examineras genom en skriftlig inlämningsuppgift som …</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker i form av skriftlig tentamen motsvarande 6 hp (U-VG) som i huvudsak examinerar lärandemål **1-7** och e…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker i form av skriftlig tentamen motsvarande 6 hp (U-VG) som i huvudsak examinerar lärandemål **1-7 **och e…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 **examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentamen. **D…</t>
+          <t>Examinationsformer skrivet som löpande text: **Delkurs 1** examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentamen. **D…</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 och 3 **examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentame…</t>
+          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 och 3** examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentame…</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar. Betyg rapporteras som ett moment. ****…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar. Betyg rapporteras som ett moment.…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker i form av skriftlig tentamen motsvarande 6 hp (U-VG) som i huvudsak examinerar lärandemål **1-7 **och e…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker i form av skriftlig tentamen motsvarande 6 hp (U-VG) som i huvudsak examinerar lärandemål **1-7** och e…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: ** Modul 1, Utveckling av undervisning** (7,5 hp, inkl 4,5 hp VFU) Exami…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Modul 1, Utveckling av undervisning** (7,5 hp, inkl 4,5 hp VFU) Examin…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar samt två skriftliga inlämningsuppgifter.****…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar samt två skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt deltagande i och dokumentation från rollspel****…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt deltagande i och dokumentation från rollspel…</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Examinationsformer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Examinationsformer'!$A$1:$E$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Examinationsformer'!$A$1:$E$504</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E485"/>
+  <dimension ref="A1:E504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7681,12 +7681,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Seminarier 1,5 hp Skriftlig inlämningsuppgift i grupp 1,5 hp Individuell skriftlig tentamen 4,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift, muntlig presentation vid seminarium, samt kritisk granskning av ett annat studentarbete.…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 2 hp Reflektionsprotokoll, 2 hp Skriftlig inlämningsuppgift 3,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom en muntlig presentation vid ett examinerande seminarium, en skriftlig inlämningsuppgift samt krit…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 4 hp Skriftlig inlämningsuppgift i grupp 3 hp Aktivt deltagande vid seminarier, 0,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom fortlöpande bedömning av skriftliga och muntliga arbeten, samt förberett och aktivt seminariedel…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande vid workshops. Genomförande och presentation av hemuppgifter (2 hp). Individuell skriftlig examination…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker via skriftliga inlämningsuppgifter och muntliga redovisningar. Examinerande övningar sker i anslutnin…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 4,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras muntligt genom fortlöpande bedömning av seminariemedverkan samt genom skriftliga inlämningsuppgifter (…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7831,24 +7831,24 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Individuell skriftlig tentamen, 4 hp Skriftlig gruppuppgift, 3,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen är både skriftlig och muntlig. Den skriftliga examinationen består av författan-det av en argumenterande t…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7858,24 +7858,24 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen, 4 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntlig presentation samt en skriftlig inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7885,24 +7885,24 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen, 3 hp Skriftlig inlämningsuppgift och seminarium 4,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga presentationer och skriftliga inlämningsuppgifter…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7912,24 +7912,24 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 3,5 hp Skriftlig inlämningsuppgift, 4 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom examinerande seminarier, kritisk granskning av texter och skriftliga uppgifter…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7939,24 +7939,24 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar, och genom framläggande av ett färdigt arbete, försvarandet…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker muntligt och genom skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7966,24 +7966,24 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar och opponentskap på andra studenters arbete. Skriftliga inl…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker muntligt och genom skriftliga inlämningsuppgifter…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7993,24 +7993,24 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar försvarandet av desamma och opponentskap på andra studenter…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga presentationer och skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8020,24 +8020,24 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Obligatoriska seminarier med muntlig redovisning av en process genomförd på en arbetsplats, 1 hp (mål 2,3,5) Obligatoris…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga presentationer och skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8047,24 +8047,24 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar individuellt och i grupp samt genom en skriftlig inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom skriftliga inlämningsuppgifter och muntliga presentationer.…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8074,24 +8074,24 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar individuellt och i grupp samt genom en skriftlig inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntlig presentation samt en skriftlig inlämningsuppgift…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8101,24 +8101,24 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventileringsseminarium, vid vilket…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom fortlöpande bedömning av skriftliga och muntliga presentationer, samt förberett och aktivt semin…</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8128,24 +8128,24 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventileringsseminarium, vid vilket…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga presentationer…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8155,24 +8155,24 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom en avslutande rapport, där statistiska analyser tillämpas på utbildningsvetenskapliga data och r…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8182,24 +8182,24 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras dels i form av muntliga redoviningar individuellt och i grupp, dels genom individuella skriftliga inlä…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga presentationer och skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter samt en individuell skrif…</t>
+          <t>Examinationsformer skrivet som löpande text: Seminarier 1,5 hp Skriftlig inlämningsuppgift i grupp 1,5 hp Individuell skriftlig tentamen 4,5 hp…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom skriftliga inlämningsuppgifter samt muntliga redovisningar vid seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 2 hp Reflektionsprotokoll, 2 hp Skriftlig inlämningsuppgift 3,5 hp…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom skriftliga inlämningsuppgifter samt muntliga redovisningar vid seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 4 hp Skriftlig inlämningsuppgift i grupp 3 hp Aktivt deltagande vid seminarier, 0,5 hp…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Modul 1, Utveckling av undervisning** (7,5 hp, inkl 4,5 hp VFU) Examin…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande vid workshops. Genomförande och presentation av hemuppgifter (2 hp). Individuell skriftlig examination…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Modul 1, Utveckling av undervisning** (7,5 hp, inkl 4,5 hp VFU) Examin…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 4,5 hp…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom muntlig presentation, enskild skriftlig uppgift samt opponering på andras skriftliga uppgif…</t>
+          <t>Examinationsformer skrivet som löpande text: Individuell skriftlig tentamen, 4 hp Skriftlig gruppuppgift, 3,5 hp…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom en eller flera muntliga redovisningar, skriftliga uppgifter och seminarier samt verksamhets…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen, 4 hp…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8398,24 +8398,24 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningar och aktivt deltagande i seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen, 3 hp Skriftlig inlämningsuppgift och seminarium 4,5 hp…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt deltagande vid seminarier samt genom en vetenskaplig uppsats som den studerande skriver s…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 3,5 hp Skriftlig inlämningsuppgift, 4 hp…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämningsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar, och genom framläggande av ett färdigt arbete, försvarandet…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8479,24 +8479,24 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar samt två skriftliga inlämningsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar och opponentskap på andra studenters arbete. Skriftliga inl…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar samt två skriftliga inlämningsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar försvarandet av desamma och opponentskap på andra studenter…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8533,19 +8533,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Moment 1, Teoretiska perspektiv på sociala relationer, konflikter och …</t>
+          <t>Examinationsformer skrivet som löpande text: Obligatoriska seminarier med muntlig redovisning av en process genomförd på en arbetsplats, 1 hp (mål 2,3,5) Obligatoris…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8560,19 +8560,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Moment 1, Teoretiska perspektiv på sociala relationer, konflikter och …</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar individuellt och i grupp samt genom en skriftlig inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8587,19 +8587,19 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen, produktion av en gestaltande uppgift samt aktivt deltagande i seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar individuellt och i grupp samt genom en skriftlig inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8614,19 +8614,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs 1 ”Ledarskap” examineras individuellt genom skriftlig hemtentamen samt i en muntligt och skriftlig examination i…</t>
+          <t>Examinationsformer skrivet som löpande text: En vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventileringsseminarium, vid vilket…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8641,19 +8641,19 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs 1 ”Ledarskap” examineras individuellt genom skriftlig hemtentamen samt i en muntligt och skriftlig examination i…</t>
+          <t>Examinationsformer skrivet som löpande text: En vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventileringsseminarium, vid vilket…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8668,19 +8668,19 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs ”Kunskap och lärande” examineras genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter i…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och seminarier.…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8695,19 +8695,19 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs ”Specialpedagogik och ämnesdidaktik” examineras genom muntlig och skriftlig presentation och diskussion av semin…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras dels i form av muntliga redoviningar individuellt och i grupp, dels genom individuella skriftliga inlä…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8722,19 +8722,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs ”Kunskap och lärande” examineras genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter i…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter samt en individuell skrif…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8749,19 +8749,19 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs ”Specialpedagogik och ämnesdidaktik” examineras genom muntlig och skriftlig presentation och diskussion av semin…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom skriftliga inlämningsuppgifter samt muntliga redovisningar vid seminarier.…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8776,19 +8776,19 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Den studerande examineras genom presentation och diskussion av seminarieuppgifter samt genom skriftliga inlämningsuppgif…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom skriftliga inlämningsuppgifter samt muntliga redovisningar vid seminarier.…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8803,19 +8803,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs 1: inlämningsuppgifter samt muntlig presentation och diskussion av seminarieuppgifter Delkurs 2: inlämningsuppgi…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Modul 1, Utveckling av undervisning** (7,5 hp, inkl 4,5 hp VFU) Examin…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8830,19 +8830,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom inlämningsuppgifter, skriftlig tentamen samt muntlig presentation och diskussion av seminar…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Modul 1, Utveckling av undervisning** (7,5 hp, inkl 4,5 hp VFU) Examin…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GPG2SH</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8857,19 +8857,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom inlämningsuppgifter, muntlig presentation och diskussion av seminarieuppgifter samt uppgift…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom muntlig presentation, enskild skriftlig uppgift samt opponering på andras skriftliga uppgif…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom inlämningsuppgifter, skriftlig tentamen samt muntlig presentation och diskussion av seminar…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom en eller flera muntliga redovisningar, skriftliga uppgifter och seminarier samt verksamhets…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8911,19 +8911,19 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs ”Utvecklingsarbete” examineras genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter sam…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningar och aktivt deltagande i seminarier.…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,19 +8938,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras muntligt och skriftligt genom ett självständigt arbete som slutligen presenteras antingen skriftligt e…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt deltagande vid seminarier samt genom en vetenskaplig uppsats som den studerande skriver s…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8965,19 +8965,19 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer saknas.…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Undersökningen rapporteras via en uppsats som den studerande ska presentera och försvara vid ett särskilt seminarium. De…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar samt två skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9019,19 +9019,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Undersökningen rapporteras via en uppsats som den studerande ska presentera och försvara vid ett särskilt seminarium. De…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar samt två skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9046,19 +9046,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Undersökningen rapporteras via en uppsats som den studerande ska presentera och försvara vid ett särskilt seminarium. De…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Moment 1, Teoretiska perspektiv på sociala relationer, konflikter och …</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9073,19 +9073,19 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar där digitala lärresurser och olika uttrycksformer används.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i tre moment enligt följande: **Moment 1, Teoretiska perspektiv på sociala relationer, konflikter och …</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9100,19 +9100,19 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar där digitala lärresurser och olika uttrycksformer används.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen, produktion av en gestaltande uppgift samt aktivt deltagande i seminarier.…</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9127,19 +9127,19 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom en reflekterande skriftlig uppgift med tydliga referenser till kurslitteraturen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs 1 ”Ledarskap” examineras individuellt genom skriftlig hemtentamen samt i en muntligt och skriftlig examination i…</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av aktivt deltagande på seminarier och genom ett skriftligt PM i vilket deltagarna analyserar o…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs 1 ”Ledarskap” examineras individuellt genom skriftlig hemtentamen samt i en muntligt och skriftlig examination i…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9181,19 +9181,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt deltagande i seminarier samt skriftliga PM.…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs ”Kunskap och lärande” examineras genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter i…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9208,19 +9208,19 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntliga presentationer och skriftlig promemoria.…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs ”Specialpedagogik och ämnesdidaktik” examineras genom muntlig och skriftlig presentation och diskussion av semin…</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Ett självständigt genomfört arbete som presenteras skriftligt i en vetenskaplig uppsats som försvaras på ett ventilering…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs ”Kunskap och lärande” examineras genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter i…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9262,24 +9262,24 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga presentationer vid aktivt deltagande i seminarier och skriftligt PM.…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs ”Specialpedagogik och ämnesdidaktik” examineras genom muntlig och skriftlig presentation och diskussion av semin…</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Studenten examineras genom obligatorisk seminariemedverkan, kontinuerliga PM och ett avslutande skriftligt arbete.…</t>
+          <t>Examinationsformer skrivet som löpande text: Den studerande examineras genom presentation och diskussion av seminarieuppgifter samt genom skriftliga inlämningsuppgif…</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av en vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventil…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs 1: inlämningsuppgifter samt muntlig presentation och diskussion av seminarieuppgifter Delkurs 2: inlämningsuppgi…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9343,24 +9343,24 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av en vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventil…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom inlämningsuppgifter, skriftlig tentamen samt muntlig presentation och diskussion av seminar…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>GPG2SH</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom ett skriftligt PM kombinerat med ett individuellt samtal med examinerande lärare.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom inlämningsuppgifter, muntlig presentation och diskussion av seminarieuppgifter samt uppgift…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SH</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom fortlöpande bedömning av förberett och aktivt deltagande i seminarier, samt avslutande skriftlig …</t>
+          <t>Examinationsformer skrivet som löpande text: Kursens mål examineras genom inlämningsuppgifter, skriftlig tentamen samt muntlig presentation och diskussion av seminar…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9424,24 +9424,24 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker i form av aktivt deltagande vid seminarier samt skriftliga inlämningsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs ”Utvecklingsarbete” examineras genom muntlig och skriftlig presentation och diskussion av seminarieuppgifter sam…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga inlämningsuppgifter, muntliga redovisningar och aktivt deltagande i seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras muntligt och skriftligt genom ett självständigt arbete som slutligen presenteras antingen skriftligt e…</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer saknas.…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
+          <t>Examinationsformer skrivet som löpande text: Undersökningen rapporteras via en uppsats som den studerande ska presentera och försvara vid ett särskilt seminarium. De…</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av ett examensarbete som den studerande presenterar och försvarar vid ett särskilt ventilerings…</t>
+          <t>Examinationsformer skrivet som löpande text: Undersökningen rapporteras via en uppsats som den studerande ska presentera och försvara vid ett särskilt seminarium. De…</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -9559,24 +9559,24 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar och skriftliga inlämningsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Undersökningen rapporteras via en uppsats som den studerande ska presentera och försvara vid ett särskilt seminarium. De…</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9586,24 +9586,24 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt deltagande i seminarier, muntliga redovisningar, skriftliga inlämningsuppgifter, uppsats …</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar där digitala lärresurser och olika uttrycksformer används.…</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -9613,24 +9613,24 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: I samtliga delkurser utgör förberett och aktivt deltagande i seminarier och muntliga och skriftliga redovisningar av til…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar där digitala lärresurser och olika uttrycksformer används.…</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -9640,24 +9640,24 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: I samtliga delkurser utgör förberett och aktivt deltagande i seminarier och muntliga och skriftliga redovisningar av til…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom en reflekterande skriftlig uppgift med tydliga referenser till kurslitteraturen.…</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -9667,24 +9667,24 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom en religionsvetenskaplig uppsats som försvaras vid ett ventileringsseminarium, samt opponering p…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av aktivt deltagande på seminarier och genom ett skriftligt PM i vilket deltagarna analyserar o…</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -9694,24 +9694,24 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom ett religionsvetenskapligt examensarbete som försvaras vid ett ventileringsseminarium, samt oppo…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt deltagande i seminarier samt skriftliga PM.…</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -9721,24 +9721,24 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras kontinuerligt genom förberett och aktivt deltagande i seminarier och skriftliga inlämningsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntliga presentationer och skriftlig promemoria.…</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -9748,24 +9748,24 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Delkurs 1** examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentamen. **D…</t>
+          <t>Examinationsformer skrivet som löpande text: Ett självständigt genomfört arbete som presenteras skriftligt i en vetenskaplig uppsats som försvaras på ett ventilering…</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -9775,19 +9775,19 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 och 3** examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentame…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga presentationer vid aktivt deltagande i seminarier och skriftligt PM.…</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9802,19 +9802,19 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursens examinationsformer består av en skriftligt redovisad forskningsplan, aktivt seminariedeltagande och ventilerings…</t>
+          <t>Examinationsformer skrivet som löpande text: Studenten examineras genom obligatorisk seminariemedverkan, kontinuerliga PM och ett avslutande skriftligt arbete.…</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9829,19 +9829,19 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av en vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventil…</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9856,19 +9856,19 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av en vetenskaplig uppsats som den studerande presenterar och försvarar vid ett särskilt ventil…</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar kombinerat med att kursen examineras genom ett eget skriftl…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom ett skriftligt PM kombinerat med ett individuellt samtal med examinerande lärare.…</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom fortlöpande bedömning av förberett och aktivt deltagande i seminarier, samt avslutande skriftlig …</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En dugga per rättsområde (4x1 hp) samt en skriftlig inlämningsuppgift med avslutande seminarium (3,5 hp).…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker i form av aktivt deltagande vid seminarier samt skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9964,24 +9964,24 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga inlämningsuppgifter, muntliga redovisningar och aktivt deltagande i seminarier.…</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -9991,24 +9991,24 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande vid seminarier samt reflektiva protokoll.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10018,24 +10018,24 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen. Muntlig tentamen kan förekomma efter samråd med examinator.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10045,24 +10045,24 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras i form av ett examensarbete som den studerande presenterar och försvarar vid ett särskilt ventilerings…</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt aktivt deltagande på seminarierna.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom muntliga redovisningar och skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt aktivt deltagande på seminarierna.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt deltagande i seminarier, muntliga redovisningar, skriftliga inlämningsuppgifter, uppsats …</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10126,24 +10126,24 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker i form skriftlig tentamen. Annan examinationsform kan förekomma efter beslut av examinator.…</t>
+          <t>Examinationsformer skrivet som löpande text: I samtliga delkurser utgör förberett och aktivt deltagande i seminarier och muntliga och skriftliga redovisningar av til…</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10153,24 +10153,24 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen sker i form av skriftlig tentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: I samtliga delkurser utgör förberett och aktivt deltagande i seminarier och muntliga och skriftliga redovisningar av til…</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10180,24 +10180,24 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt en individuella skriftlig uppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom en religionsvetenskaplig uppsats som försvaras vid ett ventileringsseminarium, samt opponering p…</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10207,24 +10207,24 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt deltagande i och dokumentation från rollspel…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom ett religionsvetenskapligt examensarbete som försvaras vid ett ventileringsseminarium, samt oppo…</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10234,24 +10234,24 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Arbete med relevant innehåll skall utföras som grupparbete med både skriftlig och muntlig redovisning samt skriftlig ten…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras kontinuerligt genom förberett och aktivt deltagande i seminarier och skriftliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10261,24 +10261,24 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen sker med separat tentamen enligt nedan för de båda resp avsnitten Obeståndsrätt 7,5 hp Muntlig eller skrif…</t>
+          <t>Examinationsformer skrivet som löpande text: **Delkurs 1** examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentamen. **D…</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10288,24 +10288,24 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker i form skriftlig tentamen 7,5 hp och inlämningsuppgift 7,5 hp.…</t>
+          <t>Examinationsformer skrivet som löpande text: **Delkurs 1 och 3** examineras genom aktivt seminariedeltagande, muntlig och skriftlig redovisning samt genom hemtentame…</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10315,24 +10315,24 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Författande av inlämningsuppgift och aktivt deltagande i seminarier 1,5 hp. Skriftlig salstentamen i slutet av kursen 6 …</t>
+          <t>Examinationsformer skrivet som löpande text: Kursens examinationsformer består av en skriftligt redovisad forskningsplan, aktivt seminariedeltagande och ventilerings…</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10342,24 +10342,24 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen (6 hp) Deltagande i obligatoriska seminarier (1,5 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10369,24 +10369,24 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämnande av besvarade frågeställningar, analyser, upprättat åtgärdscheman samt anställningsavta…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker genom förberett och aktivt deltagande i seminarier, muntliga presentationer och skriftliga inlämnings…</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10396,19 +10396,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande på seminarier och godkänd fältuppgift. Slutexamination sker i form av salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar kombinerat med att kursen examineras genom ett eget skriftl…</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10423,19 +10423,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier, genomförande av en rättsutredning och fältuppgift (1,5 hp). Individuell skriftlig slutex…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen.…</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10450,19 +10450,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (4,5 hp) samt aktivt deltagande i seminarier inklusive inlämningsuppgift (3 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: En dugga per rättsområde (4x1 hp) samt en skriftlig inlämningsuppgift med avslutande seminarium (3,5 hp).…</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10477,19 +10477,19 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen, inlämningsuppgifter samt aktivt deltagande vid seminarieverksamhet. Kursmålen …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen.…</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10504,19 +10504,19 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (4,5 hp) samt aktivt deltagande i seminarier inklusive inlämningsuppgift (3 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande vid seminarier samt reflektiva protokoll.…</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10531,19 +10531,19 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (5 hp) samt aktivt deltagande vid seminarieverksamhet (2,5 hp). Kursmålen (1), …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen. Muntlig tentamen kan förekomma efter samråd med examinator.…</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10558,19 +10558,19 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Inlämningsuppgifter samt aktivt deltagande vid seminarieverksamhet (5 hp).…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen.…</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10585,19 +10585,19 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (3 hp) samt aktivt deltagande vid seminarieverksamhet (2 hp). Kursmålen (1), (2…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt aktivt deltagande på seminarierna.…</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10612,19 +10612,19 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är duggor (3 hp) samt skriftlig hemtentamen med muntlig uppföljning (4,5hp). Kursmålen (1) och (2) ex…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt aktivt deltagande på seminarierna.…</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10639,19 +10639,19 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,5 hp).…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker i form skriftlig tentamen. Annan examinationsform kan förekomma efter beslut av examinator.…</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10666,19 +10666,19 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är aktivt deltagande vid seminarieverksamhet och inlämningsuppgifter. Kursmålen (1), (2) och (4) exam…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker i form av skriftlig tentamen.…</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10693,19 +10693,19 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen samt aktivt deltagande vid seminarieverksamhet, inklusive inlämningsuppgift. Ku…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt en individuella skriftlig uppgift.…</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10720,24 +10720,24 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen samt aktivt deltagande vid seminarieverksamhet, inklusive inlämningsuppgifter. …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen samt deltagande i och dokumentation från rollspel…</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>ASK22G</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10747,24 +10747,24 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Arbete med relevant innehåll skall utföras som grupparbete med både skriftlig och muntlig redovisning samt skriftlig ten…</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10774,24 +10774,24 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen sker med separat tentamen enligt nedan för de båda resp avsnitten Obeståndsrätt 7,5 hp Muntlig eller skrif…</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10801,24 +10801,24 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker i form skriftlig tentamen 7,5 hp och inlämningsuppgift 7,5 hp.…</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10828,24 +10828,24 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier…</t>
+          <t>Examinationsformer skrivet som löpande text: Författande av inlämningsuppgift och aktivt deltagande i seminarier 1,5 hp. Skriftlig salstentamen i slutet av kursen 6 …</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10855,24 +10855,24 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntliga redovisningar, skriftliga inlämningsuppgifter och aktivt deltagande i seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen (6 hp) Deltagande i obligatoriska seminarier (1,5 hp)…</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -10882,24 +10882,24 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämnande av besvarade frågeställningar, analyser, upprättat åtgärdscheman samt anställningsavta…</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10909,24 +10909,24 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande på seminarier och godkänd fältuppgift. Slutexamination sker i form av salstentamen.…</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10936,24 +10936,24 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier, genomförande av en rättsutredning och fältuppgift (1,5 hp). Individuell skriftlig slutex…</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10963,24 +10963,24 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (4,5 hp) samt aktivt deltagande i seminarier inklusive inlämningsuppgift (3 hp)…</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -10990,24 +10990,24 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen, inlämningsuppgifter samt aktivt deltagande vid seminarieverksamhet. Kursmålen …</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11017,24 +11017,24 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (4,5 hp) samt aktivt deltagande i seminarier inklusive inlämningsuppgift (3 hp)…</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11044,24 +11044,24 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (5 hp) samt aktivt deltagande vid seminarieverksamhet (2,5 hp). Kursmålen (1), …</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11071,24 +11071,24 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Inlämningsuppgifter samt aktivt deltagande vid seminarieverksamhet (5 hp).…</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11098,24 +11098,24 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen (3 hp) samt aktivt deltagande vid seminarieverksamhet (2 hp). Kursmålen (1), (2…</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11125,24 +11125,24 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är duggor (3 hp) samt skriftlig hemtentamen med muntlig uppföljning (4,5hp). Kursmålen (1) och (2) ex…</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11152,24 +11152,24 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
+          <t>Examinationsformer skrivet som löpande text: En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,5 hp).…</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11179,24 +11179,24 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är aktivt deltagande vid seminarieverksamhet och inlämningsuppgifter. Kursmålen (1), (2) och (4) exam…</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11206,24 +11206,24 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen samt aktivt deltagande vid seminarieverksamhet, inklusive inlämningsuppgift. Ku…</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11233,19 +11233,19 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Inlämningsuppgift och seminarium.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationsformer är skriftlig tentamen samt aktivt deltagande vid seminarieverksamhet, inklusive inlämningsuppgifter. …</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>ASK22G</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -11260,19 +11260,19 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier.…</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22G</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11287,19 +11287,19 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier…</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11314,19 +11314,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen och studentens aktiva deltagande vid seminarieverksamhet.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier…</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11341,19 +11341,19 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, en skriftlig inlämningsuppgift och studentens aktiva deltagande vid seminarieverksamhet.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier…</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11368,19 +11368,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntliga redovisningar, skriftliga inlämningsuppgifter och aktivt deltagande i seminarier.…</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11395,19 +11395,19 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>SK1058</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11422,19 +11422,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och aktivt deltagande i seminarier.…</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11449,19 +11449,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter och seminarier.…</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>SK1062</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11476,19 +11476,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen och skriftlig inlämningsuppgift samt studentens aktiva deltagande vid seminarieverksamhet.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11503,19 +11503,19 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen och skriftlig inlämningsuppgift samt studentens aktiva deltagande vid seminarieverksamhet.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11530,19 +11530,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen och skriftlig inlämningsuppgift samt studentens aktiva deltagande vid seminarieverksamhet.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11557,19 +11557,19 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom seminarier och skriftliga redovisningar.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11584,19 +11584,19 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>SK2013</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11611,19 +11611,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga arbeten och aktivt deltagande vid seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -11638,19 +11638,19 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -11670,19 +11670,19 @@
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11692,24 +11692,24 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter, aktivt deltagande på seminarier, fältuppgift samt individuell hemtentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Salstentamen och seminarium. Salstentamen kan ersättas av inlämningsuppgift.…</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11719,24 +11719,24 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Alla delkurser examineras genom aktivt deltagande vid seminarier samt muntliga och skriftliga redovisningar och skriftli…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -11746,24 +11746,24 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination görs genom aktivt deltagande i seminarier och individuell skriftlig tentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Inlämningsuppgift och seminarium.…</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11773,24 +11773,24 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar, seminarier samt skriftlig tentamen. Betyg rapporteras som …</t>
+          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11800,24 +11800,24 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen och studentens aktiva deltagande vid seminarieverksamhet.…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11827,24 +11827,24 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Fyra obligatoriska seminarier och en skriftlig salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen och studentens aktiva deltagande vid seminarieverksamhet.…</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11854,24 +11854,24 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Muntliga och skriftliga redovisningar samt en skriftlig hemtentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, en skriftlig inlämningsuppgift och studentens aktiva deltagande vid seminarieverksamhet.…</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>SO1033</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11881,24 +11881,24 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Obligatoriska seminarier och en skriftlig salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11908,24 +11908,24 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar och skriftlig salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>SO1037</t>
+          <t>SK1058</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11935,24 +11935,24 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Seminarier och en skriftlig salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1058</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11962,24 +11962,24 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga redovisningar samt salstentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>SK1062</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11989,24 +11989,24 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom grupparbetsrapporter, redovisningar och en individuell mindre uppsats. Aktivt deltagande i obliga…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen och skriftlig inlämningsuppgift samt studentens aktiva deltagande vid seminarieverksamhet.…</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1062</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -12016,24 +12016,24 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter: 5 hp Seminarier: 2,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen och skriftlig inlämningsuppgift samt studentens aktiva deltagande vid seminarieverksamhet.…</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12043,24 +12043,24 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter 5 hp Seminarier 2,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig hemtentamen och skriftlig inlämningsuppgift samt studentens aktiva deltagande vid seminarieverksamhet.…</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12070,24 +12070,24 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift. (Mål 2, 3, 4, 5, 6, 7, 8) (4,5 hp) Aktivt deltagande i seminarier och uppgift som redovisas skriftlig…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom seminarier och skriftliga redovisningar.…</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12097,24 +12097,24 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (2,5 hp) Lärandemål 3-5 examine…</t>
+          <t>Examinationsformer skrivet som löpande text: En skriftlig hemtentamen, skriftliga och muntliga redovisningar samt studentens aktiva deltagande vid seminarieverksamhe…</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>SK2013</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12124,24 +12124,24 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: 1) Individuellt skriftligt arbete, 1,5 hp 2) Inlämningsuppgift, 3 hp 3) Redovisning av grupparbete, poster presentation …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga arbeten och aktivt deltagande vid seminarier.…</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2013</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12151,24 +12151,24 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Inlämningsuppgift 2,5 hp Reflektionsprotokoll 2 hp Grupparbete 3 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar.…</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12178,24 +12178,24 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig inlämningsuppgift (5 hp) Skriftlig tentamen (5 hp) Grupparbete (5 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntlig och skriftlig redovisning av examensarbete samt granskning av annan students examensarbete.…</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12205,24 +12205,24 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Tentamen (6 hp) examinerar mål 1, 2, 3, 5, 8.…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter, aktivt deltagande på seminarier, fältuppgift samt individuell hemtentamen.…</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -12232,24 +12232,24 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen (Lärandemål 1, 2, 3, 4, 5 ) (2,5 hp) Skriftliga och muntliga inlämningsuppgifter (Lärandemål 2, 3…</t>
+          <t>Examinationsformer skrivet som löpande text: Alla delkurser examineras genom aktivt deltagande vid seminarier samt muntliga och skriftliga redovisningar och skriftli…</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12259,24 +12259,24 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande till seminarierna: 2.5 poäng Skriftliga inlämningsuppgifter: 5 poäng…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination görs genom aktivt deltagande i seminarier och individuell skriftlig tentamen.…</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12286,24 +12286,24 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift (5,5 hp) Muntlig presentation (2 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga och muntliga redovisningar, seminarier samt skriftlig tentamen. Betyg rapporteras som …</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -12313,24 +12313,24 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Seminarier (6 hp), skriftliga inlämningsuppgifter (4 hp) och slutrapport (5 hp).…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen och studentens aktiva deltagande vid seminarieverksamhet.…</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -12340,24 +12340,24 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Individuellt skriftligt arbete, 2 hp Grupparbete kring ett case, 3 hp Indivuduell skriftlig tentamen 2,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Fyra obligatoriska seminarier och en skriftlig salstentamen.…</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -12367,24 +12367,24 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Individuella skriftliga inlämningsuppgifter Aktivt deltagande i seminarier…</t>
+          <t>Examinationsformer skrivet som löpande text: Muntliga och skriftliga redovisningar samt en skriftlig hemtentamen.…</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>SO1033</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -12394,24 +12394,24 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig inlämningsuppgift, muntliga presentationer och aktivt deltagande i seminarier, skriftlig tentamen…</t>
+          <t>Examinationsformer skrivet som löpande text: Obligatoriska seminarier och en skriftlig salstentamen.…</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1033</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12421,24 +12421,24 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig och muntlig examination 5hp och aktiv deltagande vid genomförandet av projekt 2,5 hp.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom muntliga och skriftliga redovisningar och skriftlig salstentamen.…</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>SO1037</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -12448,24 +12448,24 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom deltagande i seminarier, muntliga och skriftliga uppgifter och en avslutande muntlig presentatio…</t>
+          <t>Examinationsformer skrivet som löpande text: Seminarier och en skriftlig salstentamen.…</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1037</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -12475,24 +12475,24 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen (4,5 hp, A-F) examinerar mål 1-6, 9, seminarium och inlämningsuppgift (3 hp, U-G) examinerar mål …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga redovisningar samt salstentamen.…</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12502,19 +12502,19 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig inlämningsuppgift 2 hp (U-G), muntlig redovisning vid seminarier 1,5 hp (U-G) och skriftlig salstentamen 4 hp …</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom grupparbetsrapporter, redovisningar och en individuell mindre uppsats. Aktivt deltagande i obliga…</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -12529,19 +12529,19 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Två inlämningsuppgifter (2x5 hp), två muntliga redovisningar (2x2 hp) och ett seminarium (1 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter: 5 hp Seminarier: 2,5 hp…</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -12556,19 +12556,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Tentamen (3 hp), seminarier och inlämningsuppgift (4,5 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftliga inlämningsuppgifter 5 hp Seminarier 2,5 hp…</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -12583,19 +12583,19 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (A-F, 2,5 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift. (Mål 2, 3, 4, 5, 6, 7, 8) (4,5 hp) Aktivt deltagande i seminarier och uppgift som redovisas skriftlig…</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -12610,19 +12610,19 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Seminarier och inlämningsuppgifter, 4,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (2,5 hp) Lärandemål 3-5 examine…</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -12637,19 +12637,19 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (2,5 hp) Lärandemål 3-5 examine…</t>
+          <t>Examinationsformer skrivet som löpande text: 1) Individuellt skriftligt arbete, 1,5 hp 2) Inlämningsuppgift, 3 hp 3) Redovisning av grupparbete, poster presentation …</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -12664,19 +12664,19 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen (5 hp)…</t>
+          <t>Examinationsformer skrivet som löpande text: Inlämningsuppgift 2,5 hp Reflektionsprotokoll 2 hp Grupparbete 3 hp…</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -12691,19 +12691,19 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Seminarier och inlämningsuppgifter, 4,5 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig inlämningsuppgift (5 hp) Skriftlig tentamen (5 hp) Grupparbete (5 hp)…</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -12718,19 +12718,19 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursmål 1, 2, 3, 6 och 7 examineras genom en skriftliga salstentamen, 5 poäng. Kursmål 2, 5 och 6 examineras genom en sk…</t>
+          <t>Examinationsformer skrivet som löpande text: Tentamen (6 hp) examinerar mål 1, 2, 3, 5, 8.…</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -12745,19 +12745,19 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursmål 1, 2, 3, 6 &amp; 7 examineras genom bedömning av övningar, 3 poäng Kursmål 2, 3, 4, 5, 6 &amp; 7 examineras genom en ind…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen (Lärandemål 1, 2, 3, 4, 5 ) (2,5 hp) Skriftliga och muntliga inlämningsuppgifter (Lärandemål 2, 3…</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -12772,19 +12772,19 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Mål 1-3 och 7-8 examineras genom skriftlig salstentamen (5 hp). Mål 4-6 examineras genom skriftlig inlämningsuppgift och…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande till seminarierna: 2.5 poäng Skriftliga inlämningsuppgifter: 5 poäng…</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -12799,19 +12799,19 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom fyra obligatoriska seminarium (4x1,5 hp) (lärandemål 1-4), två skriftliga inlämningsuppgifter (2…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift (5,5 hp) Muntlig presentation (2 hp)…</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -12826,19 +12826,19 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: 1) Individuellt skriftligt arbete, 1,5 hp 2) Inlämningsuppgift, 3 hp 3) Redovisning av grupparbete, poster presentation …</t>
+          <t>Examinationsformer skrivet som löpande text: Seminarier (6 hp), skriftliga inlämningsuppgifter (4 hp) och slutrapport (5 hp).…</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -12853,19 +12853,19 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: PM (3 poäng) examinerar lärandemål 1, 2, 3, 4 och 6. Muntligt presentation och seminarier (1,5 hp) examinerar lärandemål…</t>
+          <t>Examinationsformer skrivet som löpande text: Individuellt skriftligt arbete, 2 hp Grupparbete kring ett case, 3 hp Indivuduell skriftlig tentamen 2,5 hp…</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -12880,19 +12880,19 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delkurs 1: Seminarier och skriftliga inlämningsuppgifter. Delkurs 2: Inlämningsuppgifter, seminarier samt PM. Delkurs 3:…</t>
+          <t>Examinationsformer skrivet som löpande text: Individuella skriftliga inlämningsuppgifter Aktivt deltagande i seminarier…</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>TR2005</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -12907,19 +12907,19 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen består av skriftlig rapport, muntlig redovisning, aktiv opposition på ett annat examensarbete samt aktivt …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig inlämningsuppgift, muntliga presentationer och aktivt deltagande i seminarier, skriftlig tentamen…</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -12934,19 +12934,19 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier och studiebesök följt av utvärdering (3,5 hp) samt författande av en PM (4 hp).…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig och muntlig examination 5hp och aktiv deltagande vid genomförandet av projekt 2,5 hp.…</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>TR3008</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -12961,19 +12961,19 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examinationen består av en magisteruppsats eller motsvarande, aktivt deltagande i de seminarier som ingår i kursen samt …</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom deltagande i seminarier, muntliga och skriftliga uppgifter och en avslutande muntlig presentatio…</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -12988,19 +12988,19 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier, studiebesök, skriftliga inlämningsuppgifter och muntlig presentation (3,5 hp) samt förfa…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig salstentamen (4,5 hp, A-F) examinerar mål 1-6, 9, seminarium och inlämningsuppgift (3 hp, U-G) examinerar mål …</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -13015,24 +13015,24 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delmoment 1: Aktivt deltagande i seminarier, skriftliga uppgifter och skriftlig salstentamen, 4.5 hp (examinerar mål 1) …</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig inlämningsuppgift 2 hp (U-G), muntlig redovisning vid seminarier 1,5 hp (U-G) och skriftlig salstentamen 4 hp …</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -13042,24 +13042,24 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt seminariedeltagande och skriftliga uppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Två inlämningsuppgifter (2x5 hp), två muntliga redovisningar (2x2 hp) och ett seminarium (1 hp)…</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13069,24 +13069,24 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+          <t>Examinationsformer skrivet som löpande text: Tentamen (3 hp), seminarier och inlämningsuppgift (4,5 hp)…</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13096,24 +13096,24 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (A-F, 2,5 hp)…</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -13123,24 +13123,24 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt seminariedeltagande och skriftliga uppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Seminarier och inlämningsuppgifter, 4,5 hp…</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13150,24 +13150,24 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (2,5 hp) Lärandemål 3-5 examine…</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -13177,24 +13177,24 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen (5 hp)…</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13204,24 +13204,24 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom bedömning av aktivt deltagande vid seminarier samt presentation och ventilering av det egna forsk…</t>
+          <t>Examinationsformer skrivet som löpande text: Seminarier och inlämningsuppgifter, 4,5 hp…</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -13231,24 +13231,24 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom det självständiga skriftliga arbetet men även förmågan att ge och ta konstruktiv kritik under ku…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursmål 1, 2, 3, 6 och 7 examineras genom en skriftliga salstentamen, 5 poäng. Kursmål 2, 5 och 6 examineras genom en sk…</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13258,24 +13258,24 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Fyra inlämningsuppgifter som redovisas skriftligt och muntligt samt aktivt deltagande vid fyra obligatoriska seminarier.…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursmål 1, 2, 3, 6 &amp; 7 examineras genom bedömning av övningar, 3 poäng Kursmål 2, 3, 4, 5, 6 &amp; 7 examineras genom en ind…</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>AS3007</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -13285,24 +13285,24 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Studenten examineras genom obligatorisk seminariemedverkan, kontinuerliga PM och en avslutande skriftlig hemtentamen.…</t>
+          <t>Examinationsformer skrivet som löpande text: Mål 1-3 och 7-8 examineras genom skriftlig salstentamen (5 hp). Mål 4-6 examineras genom skriftlig inlämningsuppgift och…</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>AS3008</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -13312,24 +13312,24 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras dels genom muntliga och skriftliga redovisningar i samband med seminarier, dels genom tre PM om islams…</t>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom fyra obligatoriska seminarium (4x1,5 hp) (lärandemål 1-4), två skriftliga inlämningsuppgifter (2…</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -13339,24 +13339,24 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom bedömning av studenternas aktiva deltagande i kursens seminarier och skriftliga arbeten.…</t>
+          <t>Examinationsformer skrivet som löpande text: 1) Individuellt skriftligt arbete, 1,5 hp 2) Inlämningsuppgift, 3 hp 3) Redovisning av grupparbete, poster presentation …</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>AS3010</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -13366,24 +13366,24 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämnandet av en självständigt författad, kritiskt analyserande samt jämförande litteraturstudie…</t>
+          <t>Examinationsformer skrivet som löpande text: PM (3 poäng) examinerar lärandemål 1, 2, 3, 4 och 6. Muntligt presentation och seminarier (1,5 hp) examinerar lärandemål…</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -13393,24 +13393,24 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga examinationsuppgifter.…</t>
+          <t>Examinationsformer skrivet som löpande text: Delkurs 1: Seminarier och skriftliga inlämningsuppgifter. Delkurs 2: Inlämningsuppgifter, seminarier samt PM. Delkurs 3:…</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>TR2005</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -13420,24 +13420,24 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom aktivt deltagande vid seminarier samt presentation och ventilering av det egna forskningsprojekte…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen består av skriftlig rapport, muntlig redovisning, aktiv opposition på ett annat examensarbete samt aktivt …</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>AS4001</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -13447,24 +13447,24 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom att den studerande skriver en kommenterad bibliografi.…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier och studiebesök följt av utvärdering (3,5 hp) samt författande av en PM (4 hp).…</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>AS4002</t>
+          <t>TR3008</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13474,24 +13474,24 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämning av skriftliga PM och muntliga redovisningar.…</t>
+          <t>Examinationsformer skrivet som löpande text: Examinationen består av en magisteruppsats eller motsvarande, aktivt deltagande i de seminarier som ingår i kursen samt …</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -13501,44 +13501,557 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämning av skriftliga PM och muntliga redovisningar.…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande i seminarier, studiebesök, skriftliga inlämningsuppgifter och muntlig presentation (3,5 hp) samt förfa…</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
+          <t>TR3010</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Delmoment 1: Aktivt deltagande i seminarier, skriftliga uppgifter och skriftlig salstentamen, 4.5 hp (examinerar mål 1) …</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>AS2001</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt seminariedeltagande och skriftliga uppgifter.…</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>AS2003</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>AS3001</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom aktivt seminariedeltagande och skriftliga uppgifter.…</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker fortlöpande genom aktivt deltagande vid seminarier, vid presentationer av aktuella forskningsresultat s…</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom bedömning av aktivt deltagande vid seminarier samt presentation och ventilering av det egna forsk…</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom det självständiga skriftliga arbetet men även förmågan att ge och ta konstruktiv kritik under ku…</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Fyra inlämningsuppgifter som redovisas skriftligt och muntligt samt aktivt deltagande vid fyra obligatoriska seminarier.…</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>AS3007</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Studenten examineras genom obligatorisk seminariemedverkan, kontinuerliga PM och en avslutande skriftlig hemtentamen.…</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>AS3008</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras dels genom muntliga och skriftliga redovisningar i samband med seminarier, dels genom tre PM om islams…</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom bedömning av studenternas aktiva deltagande i kursens seminarier och skriftliga arbeten.…</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>AS3010</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämnandet av en självständigt författad, kritiskt analyserande samt jämförande litteraturstudie…</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>AS3011</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom skriftliga examinationsuppgifter.…</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom aktivt deltagande vid seminarier samt presentation och ventilering av det egna forskningsprojekte…</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>AS4001</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Kursen examineras genom att den studerande skriver en kommenterad bibliografi.…</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>AS4002</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämning av skriftliga PM och muntliga redovisningar.…</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämning av skriftliga PM och muntliga redovisningar.…</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
         <is>
           <t>Examinationsformer skrivet som löpande text: Kursen examineras genom det självständiga skriftliga arbetet, men även förmågan att ge och ta konstruktiv kritik under k…</t>
         </is>
       </c>
-      <c r="E485" s="2" t="inlineStr">
+      <c r="E504" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E485"/>
+  <autoFilter ref="A1:E504"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -14508,6 +15021,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E484" r:id="rId966"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A485" r:id="rId967"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E485" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A486" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E486" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A487" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E487" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A488" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E488" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A489" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E489" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A490" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E490" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A491" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E491" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A492" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E492" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A493" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E493" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A494" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E494" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A495" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E495" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A496" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E496" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A497" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E497" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A498" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E498" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A499" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E499" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A500" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E500" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A501" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E501" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A502" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E502" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A503" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E503" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A504" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E504" r:id="rId1006"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Delmoment 1 (examinerar mål 1, 2) Individuell skriftlig dugga, 3 hp Delmoment 2 (examinerar mål 3, 4): Skriftlig inlämni…</t>
+          <t>Examinationsformer skrivet som löpande text: Delmoment 1 (examinerar mål 1, 2) Individuell skriftlig dugga, 3 hp…</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Examinationsformer.xlsx
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 3,5 hp Skriftlig inlämningsuppgift, 4 hp…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig tentamen, 3,5 hp…</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämnande av besvarade frågeställningar, analyser, upprättat åtgärdscheman samt anställningsavta…</t>
+          <t>Examinationsformer skrivet som löpande text: Examination sker genom inlämnande av besvarade frågeställningar, analyser, upprättat åtgärdsscheman samt anställningsavt…</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,5 hp).…</t>
+          <t>Examinationsformer skrivet som löpande text: En kortare dugga per rättsområde (4x1 hp) samt en skriftlig inlämningsuppgift med avslutande seminarie (3,5 hp).…</t>
         </is>
       </c>
       <c r="G397" s="2" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift. (Mål 2, 3, 4, 5, 6, 7, 8) (4,5 hp) Aktivt deltagande i seminarier och uppgift som redovisas skriftlig…</t>
+          <t>Examinationsformer skrivet som löpande text: Skriftlig uppgift. (Mål 2, 3, 4, 5, 6, 7, 8) (4,5 hp)…</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (2,5 hp) Lärandemål 3-5 examine…</t>
+          <t>Examinationsformer skrivet som löpande text: Lärandemål 1-2 examineras genom skriftlig tentamen samt aktivt deltagande på seminarier. (2,5 hp)…</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande till seminarierna: 2.5 poäng Skriftliga inlämningsuppgifter: 5 poäng…</t>
+          <t>Examinationsformer skrivet som löpande text: Aktivt deltagande till seminarierna: 2.5 poäng…</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
